--- a/artfynd/A 23153-2022 artfynd.xlsx
+++ b/artfynd/A 23153-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 23153-2022 artfynd.xlsx
+++ b/artfynd/A 23153-2022 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>80699110</v>
       </c>
       <c r="B2" t="n">
-        <v>90074</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>624743.2673790288</v>
+        <v>624743</v>
       </c>
       <c r="R2" t="n">
-        <v>6656719.257375077</v>
+        <v>6656719</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2019-10-28</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2019-10-28</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,12 +785,7 @@
         <v>80699105</v>
       </c>
       <c r="B3" t="n">
-        <v>4711</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4775</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -842,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>624644.7294588941</v>
+        <v>624645</v>
       </c>
       <c r="R3" t="n">
-        <v>6656832.958769508</v>
+        <v>6656833</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -875,19 +855,9 @@
           <t>2019-10-28</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2019-10-28</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -924,15 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>80699112</v>
+        <v>80699107</v>
       </c>
       <c r="B4" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4775</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -940,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100526</v>
+        <v>100299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -969,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>624743.2673790288</v>
+        <v>624727</v>
       </c>
       <c r="R4" t="n">
-        <v>6656719.257375077</v>
+        <v>6656811</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1002,19 +967,9 @@
           <t>2019-10-28</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2019-10-28</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1051,15 +1006,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>80699108</v>
+        <v>80699106</v>
       </c>
       <c r="B5" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>624727.1265367367</v>
+        <v>624645</v>
       </c>
       <c r="R5" t="n">
-        <v>6656811.240463321</v>
+        <v>6656833</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1129,19 +1079,9 @@
           <t>2019-10-28</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2019-10-28</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1178,15 +1118,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>80699107</v>
+        <v>80699108</v>
       </c>
       <c r="B6" t="n">
-        <v>4711</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1194,21 +1129,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100299</v>
+        <v>100526</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1223,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>624727.1265367367</v>
+        <v>624727</v>
       </c>
       <c r="R6" t="n">
-        <v>6656811.240463321</v>
+        <v>6656811</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1256,19 +1191,9 @@
           <t>2019-10-28</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2019-10-28</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1305,15 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>80699106</v>
+        <v>80699112</v>
       </c>
       <c r="B7" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1350,10 +1270,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>624644.7294588941</v>
+        <v>624743</v>
       </c>
       <c r="R7" t="n">
-        <v>6656832.958769508</v>
+        <v>6656719</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1383,19 +1303,9 @@
           <t>2019-10-28</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2019-10-28</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1435,12 +1345,7 @@
         <v>80699109</v>
       </c>
       <c r="B8" t="n">
-        <v>6203</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>6275</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1476,10 +1381,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>624739.5328835499</v>
+        <v>624740</v>
       </c>
       <c r="R8" t="n">
-        <v>6656785.152314226</v>
+        <v>6656785</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1509,19 +1414,9 @@
           <t>2019-10-28</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2019-10-28</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
